--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -428,11 +428,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -480,22 +480,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TC_MOB_INPU_008</t>
+          <t>TC_MOB_AUTH_010</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mobile - Input Validation</t>
+          <t>Mobile - Authentication</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Verify Mobile Input Validation - Step 8</t>
+          <t>Verify Mobile Authentication - Scenario 10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.091</v>
+        <v>0.047</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Failure in Input Validation step 8: Mobile UI assertion or element response timeout</t>
+          <t>Mobile UI assertion timeout or layout boundary overflow in Authentication step 10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TC_MOB_FILE_002</t>
+          <t>TC_MOB_AUTH_025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mobile - File Upload</t>
+          <t>Mobile - Authentication</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Verify Mobile File Upload - Step 2</t>
+          <t>Verify Mobile Authentication - Scenario 25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,33 +539,33 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Failure in File Upload step 2: Mobile UI assertion or element response timeout</t>
+          <t>Mobile UI assertion timeout or layout boundary overflow in Authentication step 25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TC_WEB_FORM_008</t>
+          <t>TC_MOB_NAVI_018</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Web - Forms</t>
+          <t>Mobile - Navigation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verify Live Web Forms - Scenario 8 on https://Sandeepreddy1006.github.io/DermaAI/</t>
+          <t>Verify Mobile Navigation - Scenario 18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -574,33 +574,33 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.089</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Verification failed on live deployment https://Sandeepreddy1006.github.io/DermaAI/: Expected DOM state mismatch on step 8</t>
+          <t>Mobile UI assertion timeout or layout boundary overflow in Navigation step 18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TC_WEB_FILE_002</t>
+          <t>TC_MOB_FORM_008</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Web - File Upload</t>
+          <t>Mobile - Forms</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Verify Live Web File Upload - Scenario 2 on https://Sandeepreddy1006.github.io/DermaAI/</t>
+          <t>Verify Mobile Forms - Scenario 8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -609,33 +609,33 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.149</v>
+        <v>0.054</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Verification failed on live deployment https://Sandeepreddy1006.github.io/DermaAI/: Expected DOM state mismatch on step 2</t>
+          <t>Mobile UI assertion timeout or layout boundary overflow in Forms step 8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TC_SEC_INJE_012</t>
+          <t>TC_MOB_FORM_019</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Security - Injection Tests</t>
+          <t>Mobile - Forms</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Audit Injection Tests - Probe #12</t>
+          <t>Verify Mobile Forms - Scenario 19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -644,28 +644,28 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.011</v>
+        <v>0.117</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Security check flag: Potential flaw identified in Injection Tests step 12</t>
+          <t>Mobile UI assertion timeout or layout boundary overflow in Forms step 19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TC_SEC_CONF_005</t>
+          <t>TC_MOB_CRUD_014</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Security - Configuration Tests</t>
+          <t>Mobile - CRUD Operations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Audit Configuration Tests - Probe #5</t>
+          <t>Verify Mobile CRUD Operations - Scenario 14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -679,11 +679,1866 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.033</v>
+        <v>0.077</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Security check flag: Potential flaw identified in Configuration Tests step 5</t>
+          <t>Mobile UI assertion timeout or layout boundary overflow in CRUD Operations step 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC_MOB_CRUD_028</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mobile - CRUD Operations</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Verify Mobile CRUD Operations - Scenario 28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Mobile UI assertion timeout or layout boundary overflow in CRUD Operations step 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TC_MOB_INPU_005</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mobile - Input Validation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Verify Mobile Input Validation - Scenario 5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Mobile UI assertion timeout or layout boundary overflow in Input Validation step 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC_MOB_INPU_012</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mobile - Input Validation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Verify Mobile Input Validation - Scenario 12</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Mobile UI assertion timeout or layout boundary overflow in Input Validation step 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC_MOB_FILE_002</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mobile - File Upload</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Verify Mobile File Upload - Scenario 2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Mobile UI assertion timeout or layout boundary overflow in File Upload step 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC_MOB_FILE_007</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mobile - File Upload</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Verify Mobile File Upload - Scenario 7</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Mobile UI assertion timeout or layout boundary overflow in File Upload step 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC_MOB_OFFL_003</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mobile - Offline Handling</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Verify Mobile Offline Handling - Scenario 3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Mobile UI assertion timeout or layout boundary overflow in Offline Handling step 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TC_WEB_AUTH_015</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Web - Authentication</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Verify Live Web Authentication - Scenario 15</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DOM element condition or CSS selector mismatch on live deployment step 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC_WEB_AUTH_029</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Web - Authentication</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Verify Live Web Authentication - Scenario 29</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DOM element condition or CSS selector mismatch on live deployment step 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC_WEB_UI V_012</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Web - UI Validation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Verify Live Web UI Validation - Scenario 12</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DOM element condition or CSS selector mismatch on live deployment step 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TC_WEB_UI V_033</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Web - UI Validation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Verify Live Web UI Validation - Scenario 33</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DOM element condition or CSS selector mismatch on live deployment step 33</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TC_WEB_FORM_006</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Web - Forms</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Verify Live Web Forms - Scenario 6</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DOM element condition or CSS selector mismatch on live deployment step 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TC_WEB_FORM_021</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Web - Forms</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Verify Live Web Forms - Scenario 21</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DOM element condition or CSS selector mismatch on live deployment step 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TC_WEB_CRUD_010</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Web - CRUD Operations</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Verify Live Web CRUD Operations - Scenario 10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DOM element condition or CSS selector mismatch on live deployment step 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TC_WEB_CRUD_027</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Web - CRUD Operations</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Verify Live Web CRUD Operations - Scenario 27</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DOM element condition or CSS selector mismatch on live deployment step 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TC_WEB_FILE_003</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Web - File Upload</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Verify Live Web File Upload - Scenario 3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DOM element condition or CSS selector mismatch on live deployment step 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TC_WEB_FILE_014</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Web - File Upload</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Verify Live Web File Upload - Scenario 14</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DOM element condition or CSS selector mismatch on live deployment step 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TC_WEB_RESP_005</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Web - Responsive Design</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Verify Live Web Responsive Design - Scenario 5</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DOM element condition or CSS selector mismatch on live deployment step 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TC_BE_USER_008</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Backend - User Registration &amp; Auth API</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Verify API Endpoint User Registration &amp; Auth API - Probe #8</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>HTTP response 500 or JSON schema validation constraint error on probe #8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TC_BE_USER_027</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Backend - User Registration &amp; Auth API</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Verify API Endpoint User Registration &amp; Auth API - Probe #27</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>HTTP response 500 or JSON schema validation constraint error on probe #27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TC_BE_SKIN_012</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Backend - Skin Analysis Neural Endpoint</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Verify API Endpoint Skin Analysis Neural Endpoint - Probe #12</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>HTTP response 500 or JSON schema validation constraint error on probe #12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TC_BE_SKIN_034</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Backend - Skin Analysis Neural Endpoint</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Verify API Endpoint Skin Analysis Neural Endpoint - Probe #34</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>HTTP response 500 or JSON schema validation constraint error on probe #34</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TC_BE_DOCT_015</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Backend - Doctor Discovery &amp; GIS API</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Verify API Endpoint Doctor Discovery &amp; GIS API - Probe #15</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>HTTP response 500 or JSON schema validation constraint error on probe #15</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TC_BE_DOCT_042</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Backend - Doctor Discovery &amp; GIS API</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Verify API Endpoint Doctor Discovery &amp; GIS API - Probe #42</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>HTTP response 500 or JSON schema validation constraint error on probe #42</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TC_BE_HIST_018</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Backend - History &amp; Analysis Details API</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Verify API Endpoint History &amp; Analysis Details API - Probe #18</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>HTTP response 500 or JSON schema validation constraint error on probe #18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TC_BE_HIST_051</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Backend - History &amp; Analysis Details API</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Verify API Endpoint History &amp; Analysis Details API - Probe #51</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>HTTP response 500 or JSON schema validation constraint error on probe #51</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TC_BE_PASS_011</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Backend - Password Reset &amp; Verification API</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Verify API Endpoint Password Reset &amp; Verification API - Probe #11</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>HTTP response 500 or JSON schema validation constraint error on probe #11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TC_SEC_AUTH_012</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Security - Authentication Security</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Audit Security Authentication Security - Probe #12</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #12</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TC_SEC_AUTH_028</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Security - Authentication Security</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Audit Security Authentication Security - Probe #28</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TC_SEC_AUTH_015</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Security - Authorization &amp; RBAC Probes</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Audit Security Authorization &amp; RBAC Probes - Probe #15</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #15</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TC_SEC_AUTH_037</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Security - Authorization &amp; RBAC Probes</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Audit Security Authorization &amp; RBAC Probes - Probe #37</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #37</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TC_SEC_INPU_009</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Security - Input Validation &amp; Sanitization</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Audit Security Input Validation &amp; Sanitization - Probe #9</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TC_SEC_INPU_022</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Security - Input Validation &amp; Sanitization</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Audit Security Input Validation &amp; Sanitization - Probe #22</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #22</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TC_SEC_INJE_008</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Security - Injection Vulnerabilities (SQL/NoSQL/Cmd)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Audit Security Injection Vulnerabilities (SQL/NoSQL/Cmd) - Probe #8</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #8</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC_SEC_INJE_024</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Security - Injection Vulnerabilities (SQL/NoSQL/Cmd)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Audit Security Injection Vulnerabilities (SQL/NoSQL/Cmd) - Probe #24</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #24</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC_SEC_INJE_041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Security - Injection Vulnerabilities (SQL/NoSQL/Cmd)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Audit Security Injection Vulnerabilities (SQL/NoSQL/Cmd) - Probe #41</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #41</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TC_SEC_BUSI_019</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Security - Business Logic Flaws</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Audit Security Business Logic Flaws - Probe #19</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #19</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TC_SEC_SECU_005</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Security - Security Misconfiguration &amp; CORS</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Audit Security Security Misconfiguration &amp; CORS - Probe #5</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TC_SEC_SECU_018</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Security - Security Misconfiguration &amp; CORS</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Audit Security Security Misconfiguration &amp; CORS - Probe #18</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TC_SEC_SECU_032</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Security - Security Misconfiguration &amp; CORS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Audit Security Security Misconfiguration &amp; CORS - Probe #32</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #32</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TC_SEC_DAST_014</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Security - DAST Active Payload Testing</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Audit Security DAST Active Payload Testing - Probe #14</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TC_SEC_DAST_030</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Security - DAST Active Payload Testing</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Audit Security DAST Active Payload Testing - Probe #30</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Security vulnerability flag or non-compliant configuration detected in probe #30</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TC_PERF_STRE_042</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Performance - Stress 200 VU Load Testing</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Verify Performance Stress 200 VU Load Testing - Probe #42</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Response latency exceeded P95 SLA limit or socket connection queue filled on probe #42</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TC_PERF_STRE_012</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Performance - Stress 500 VU Load Testing</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Verify Performance Stress 500 VU Load Testing - Probe #12</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Response latency exceeded P95 SLA limit or socket connection queue filled on probe #12</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TC_PERF_STRE_035</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Performance - Stress 500 VU Load Testing</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Verify Performance Stress 500 VU Load Testing - Probe #35</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Response latency exceeded P95 SLA limit or socket connection queue filled on probe #35</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TC_PERF_STRE_048</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Performance - Stress 500 VU Load Testing</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Verify Performance Stress 500 VU Load Testing - Probe #48</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Response latency exceeded P95 SLA limit or socket connection queue filled on probe #48</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TC_PERF_SPIK_014</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Performance - Spike 50 to 500 VU Burst Probe</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Verify Performance Spike 50 to 500 VU Burst Probe - Probe #14</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Response latency exceeded P95 SLA limit or socket connection queue filled on probe #14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TC_PERF_SPIK_039</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Performance - Spike 50 to 500 VU Burst Probe</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Verify Performance Spike 50 to 500 VU Burst Probe - Probe #39</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Response latency exceeded P95 SLA limit or socket connection queue filled on probe #39</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TC_PERF_RPS _010</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Performance - RPS &amp; Latency Threshold Probes</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Verify Performance RPS &amp; Latency Threshold Probes - Probe #10</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Response latency exceeded P95 SLA limit or socket connection queue filled on probe #10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TC_PERF_RPS _029</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Performance - RPS &amp; Latency Threshold Probes</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Verify Performance RPS &amp; Latency Threshold Probes - Probe #29</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Response latency exceeded P95 SLA limit or socket connection queue filled on probe #29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TC_PERF_DATA_016</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Performance - Database Connection Pool Stress</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Verify Performance Database Connection Pool Stress - Probe #16</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Response latency exceeded P95 SLA limit or socket connection queue filled on probe #16</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TC_PERF_DATA_033</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Performance - Database Connection Pool Stress</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Verify Performance Database Connection Pool Stress - Probe #33</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Response latency exceeded P95 SLA limit or socket connection queue filled on probe #33</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TC_PERF_CONC_008</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Performance - Concurrent Upload Throughput Test</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Verify Performance Concurrent Upload Throughput Test - Probe #8</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Response latency exceeded P95 SLA limit or socket connection queue filled on probe #8</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TC_PERF_CONC_022</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Performance - Concurrent Upload Throughput Test</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Verify Performance Concurrent Upload Throughput Test - Probe #22</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Response latency exceeded P95 SLA limit or socket connection queue filled on probe #22</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.047</v>
+        <v>0.097</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.074</v>
+        <v>0.121</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.089</v>
+        <v>0.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.054</v>
+        <v>0.119</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.117</v>
+        <v>0.095</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.077</v>
+        <v>0.132</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.045</v>
+        <v>0.101</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.116</v>
+        <v>0.062</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.05</v>
+        <v>0.143</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.1</v>
+        <v>0.123</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.149</v>
+        <v>0.135</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.12</v>
+        <v>0.153</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.043</v>
+        <v>0.061</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.135</v>
+        <v>0.037</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.047</v>
+        <v>0.141</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.081</v>
+        <v>0.115</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.148</v>
+        <v>0.115</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.053</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.14</v>
+        <v>0.136</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.132</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.124</v>
+        <v>0.08</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.055</v>
+        <v>0.034</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.038</v>
+        <v>0.107</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.118</v>
+        <v>0.111</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.105</v>
+        <v>0.028</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.104</v>
+        <v>0.115</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.062</v>
+        <v>0.091</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.06</v>
+        <v>0.042</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.118</v>
+        <v>0.078</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.028</v>
+        <v>0.117</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.06</v>
+        <v>0.083</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0.107</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.03</v>
+        <v>0.034</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0.053</v>
+        <v>0.076</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.057</v>
+        <v>0.077</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.079</v>
+        <v>0.073</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.012</v>
+        <v>0.045</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.036</v>
+        <v>0.015</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0.019</v>
+        <v>0.05</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0.019</v>
+        <v>0.037</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0.064</v>
+        <v>0.079</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0.05</v>
+        <v>0.034</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.043</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.078</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0.017</v>
+        <v>0.077</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.076</v>
+        <v>0.06</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.256</v>
+        <v>0.167</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.132</v>
+        <v>0.305</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.205</v>
+        <v>0.231</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.161</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.132</v>
+        <v>0.281</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.244</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.122</v>
+        <v>0.288</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.107</v>
+        <v>0.097</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.125</v>
+        <v>0.11</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.134</v>
+        <v>0.245</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.211</v>
+        <v>0.236</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
